--- a/data/trans_bre/IP04D$notiene-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$notiene-Estudios-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 6,35</t>
+          <t>-8,74; 6,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 12,97</t>
+          <t>-12,02; 12,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 36,37</t>
+          <t>-4,62; 37,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-62,06; 102,89</t>
+          <t>-58,31; 97,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,77; 68,45</t>
+          <t>-43,97; 74,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-39,57; 479,75</t>
+          <t>-39,34; 512,02</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 1,35</t>
+          <t>-2,75; 1,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 2,34</t>
+          <t>-5,28; 2,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 3,66</t>
+          <t>-6,1; 3,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-54,5; 50,09</t>
+          <t>-55,53; 48,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,71; 18,32</t>
+          <t>-31,41; 15,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,47; 31,53</t>
+          <t>-36,28; 30,42</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 5,41</t>
+          <t>-0,52; 5,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 1,98</t>
+          <t>-8,55; 1,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 2,53</t>
+          <t>-10,36; 3,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-56,03; 1380,38</t>
+          <t>-42,61; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-60,43; 18,0</t>
+          <t>-58,18; 19,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-58,83; 26,53</t>
+          <t>-55,5; 37,48</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,81</t>
+          <t>-1,84; 1,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 1,19</t>
+          <t>-4,98; 1,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 3,61</t>
+          <t>-4,66; 3,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,72; 60,73</t>
+          <t>-36,1; 55,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,75; 8,85</t>
+          <t>-30,4; 9,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,07; 30,51</t>
+          <t>-29,57; 28,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$notiene-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$notiene-Estudios-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 6,11</t>
+          <t>-8,86; 6,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 12,11</t>
+          <t>-12,24; 12,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 37,59</t>
+          <t>-2,73; 37,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-58,31; 97,57</t>
+          <t>-57,41; 121,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-43,97; 74,47</t>
+          <t>-41,74; 75,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-39,34; 512,02</t>
+          <t>-29,72; 556,72</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 1,49</t>
+          <t>-2,69; 1,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 2,02</t>
+          <t>-5,12; 2,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 3,74</t>
+          <t>-5,98; 3,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-55,53; 48,6</t>
+          <t>-53,66; 49,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,41; 15,93</t>
+          <t>-30,73; 15,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,28; 30,42</t>
+          <t>-34,9; 30,96</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 5,53</t>
+          <t>-0,61; 5,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 1,61</t>
+          <t>-8,66; 1,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 3,24</t>
+          <t>-9,98; 3,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-42,61; —</t>
+          <t>-60,93; 1255,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-58,18; 19,78</t>
+          <t>-59,19; 20,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-55,5; 37,48</t>
+          <t>-54,08; 44,49</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,78</t>
+          <t>-1,7; 1,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 1,24</t>
+          <t>-4,82; 1,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 3,48</t>
+          <t>-4,44; 3,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,1; 55,37</t>
+          <t>-35,67; 57,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 9,73</t>
+          <t>-28,7; 7,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 28,98</t>
+          <t>-27,32; 30,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$notiene-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$notiene-Estudios-trans_bre.xlsx
@@ -518,8 +518,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no dispone de calefacción en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -604,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12,7</t>
+          <t>2,4</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>101,42%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -632,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 6,61</t>
+          <t>-8,96; 6,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 12,7</t>
+          <t>-11,86; 12,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 37,98</t>
+          <t>-8,43; 13,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-57,41; 121,79</t>
+          <t>-62,06; 102,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,74; 75,99</t>
+          <t>-41,77; 68,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,72; 556,72</t>
+          <t>-52,19; 222,89</t>
         </is>
       </c>
     </row>
@@ -684,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-1,03</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -699,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-7,33%</t>
+          <t>-0,24%</t>
         </is>
       </c>
     </row>
@@ -712,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,32</t>
+          <t>-2,78; 1,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 2,04</t>
+          <t>-5,1; 2,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 3,67</t>
+          <t>-3,82; 3,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-53,66; 49,34</t>
+          <t>-54,5; 50,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,73; 15,25</t>
+          <t>-29,71; 18,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,9; 30,96</t>
+          <t>-25,93; 35,08</t>
         </is>
       </c>
     </row>
@@ -764,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-3,14</t>
+          <t>-2,12</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-22,51%</t>
+          <t>-17,03%</t>
         </is>
       </c>
     </row>
@@ -792,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 5,41</t>
+          <t>-0,67; 5,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 1,29</t>
+          <t>-8,76; 1,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 3,95</t>
+          <t>-8,45; 3,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-60,93; 1255,32</t>
+          <t>-56,03; 1380,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-59,19; 20,72</t>
+          <t>-60,43; 18,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,08; 44,49</t>
+          <t>-55,35; 39,83</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>-0,34</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-2,66%</t>
+          <t>-2,7%</t>
         </is>
       </c>
     </row>
@@ -872,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 1,7</t>
+          <t>-1,66; 1,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 1,08</t>
+          <t>-4,68; 1,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 3,69</t>
+          <t>-3,48; 2,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,67; 57,94</t>
+          <t>-33,72; 60,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,7; 7,65</t>
+          <t>-28,75; 8,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,32; 30,75</t>
+          <t>-24,43; 27,89</t>
         </is>
       </c>
     </row>
